--- a/data/2026/testimonials2026.xlsx
+++ b/data/2026/testimonials2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B039FAA2-5EC6-431B-BBCB-9184FB9A0986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24A6AAA-4BDA-497D-B6B1-B9363A22C912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
     <t>Opening of registration and thanks to the organizers</t>
   </si>
   <si>
-    <t>https://www.linkedin.com/posts/kasparrufibach_we-did-it-again-the-registration-for-the-share-7434538478236954624-ZRhU?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+    <t>https://www.linkedin.com/posts/kasparrufibach_we-did-it-again-the-registration-for-the-activity-7434543762435043330-myiL?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
   </si>
 </sst>
 </file>
